--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487667_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487667_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4768</v>
+        <v>3.3122</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8767</v>
+        <v>2.9008</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6001</v>
+        <v>0.4114</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9115</v>
+        <v>0.3631</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8285</v>
+        <v>-1.4632</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.917</v>
+        <v>1.8263</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2844</v>
+        <v>1.2881</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5962</v>
+        <v>-0.5437</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.3118</v>
+        <v>1.8319</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6271</v>
+        <v>-0.925</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2323</v>
+        <v>-0.9195</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3948</v>
+        <v>-0.0056</v>
       </c>
       <c r="P2" t="n">
-        <v>0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1344</v>
+        <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>1.207</v>
+        <v>0.3398</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2505</v>
+        <v>0.3768</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0435</v>
+        <v>-0.037</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.8358</v>
+        <v>2.2212</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2821</v>
+        <v>2.4</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.1179</v>
+        <v>-0.1788</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4515</v>
+        <v>2.0641</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2581</v>
+        <v>1.4367</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1934</v>
+        <v>0.6274</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3631</v>
+        <v>2.9115</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4632</v>
+        <v>3.8285</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8263</v>
+        <v>-0.917</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2881</v>
+        <v>2.2844</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5437</v>
+        <v>3.5962</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8319</v>
+        <v>-1.3118</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.925</v>
+        <v>0.6271</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9195</v>
+        <v>0.2323</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0056</v>
+        <v>0.3948</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5523</v>
+        <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5209</v>
+        <v>0.7944</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2658</v>
+        <v>0.8106</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.255</v>
+        <v>-0.0162</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2212</v>
+        <v>-1.8358</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4</v>
+        <v>0.2821</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1788</v>
+        <v>-2.1179</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2141</v>
+        <v>0.5702</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5033</v>
+        <v>1.3933</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7174</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1842</v>
+        <v>1.1183</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2747</v>
+        <v>0.3987</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0905</v>
+        <v>0.7196</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4359</v>
+        <v>1.7935</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6488</v>
+        <v>1.0628</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2129</v>
+        <v>0.7307</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2517</v>
+        <v>-0.6752</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.374</v>
+        <v>-0.6641</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1223</v>
+        <v>-0.0111</v>
       </c>
       <c r="P4" t="n">
-        <v>0.194</v>
+        <v>2.1344</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3284</v>
+        <v>2.1344</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.7548</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1951</v>
+        <v>0.5894</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2864</v>
+        <v>0.1655</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0728</v>
+        <v>-3.4373</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.9896</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0728</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>J. LARREA IBARBURU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2095</v>
+        <v>0.4291</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9509</v>
+        <v>-2.168</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7413999999999999</v>
+        <v>2.5971</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1183</v>
+        <v>-0.0127</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3987</v>
+        <v>1.5711</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7196</v>
+        <v>-1.5838</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7935</v>
+        <v>-0.2948</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0628</v>
+        <v>1.5448</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7307</v>
+        <v>-1.8396</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6752</v>
+        <v>0.2821</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6641</v>
+        <v>0.0263</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0111</v>
+        <v>0.2558</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1344</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q5" t="n">
+        <v>-2.9105</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.3284</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.0134</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.1344</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.3941</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.1469</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.2472</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-3.4373</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.9896</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-2.4477</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LARREA IBARBURU</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1166</v>
+        <v>-0.277</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.5895</v>
+        <v>-0.8036</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7061</v>
+        <v>0.5266</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0127</v>
+        <v>1.1842</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5711</v>
+        <v>2.2747</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5838</v>
+        <v>-1.0905</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2948</v>
+        <v>1.4359</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5448</v>
+        <v>2.6488</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8396</v>
+        <v>-1.2129</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2821</v>
+        <v>-0.2517</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0263</v>
+        <v>-0.374</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2558</v>
+        <v>0.1223</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9105</v>
+        <v>-2.1344</v>
       </c>
       <c r="R6" t="n">
         <v>2.3284</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1826</v>
+        <v>-0.5824</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2782</v>
+        <v>-0.1052</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0956</v>
+        <v>-0.4772</v>
       </c>
       <c r="V6" t="n">
-        <v>0.894</v>
+        <v>-1.0728</v>
       </c>
       <c r="W6" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0728</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. JIMÉNEZ BARRETO</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.698</v>
+        <v>-0.784</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5336</v>
+        <v>-1.3987</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2316</v>
+        <v>0.6147</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8194</v>
+        <v>-1.9508</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2043</v>
+        <v>0.0395</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6151</v>
+        <v>-1.9903</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3815</v>
+        <v>-0.6692</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0824</v>
+        <v>1.31</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2991</v>
+        <v>-1.9792</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5621</v>
+        <v>-1.2816</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1219</v>
+        <v>-1.2704</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.0111</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>-2.1344</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1642</v>
+        <v>2.1344</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7647</v>
+        <v>-0.4425</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0924</v>
+        <v>-0.0533</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3277</v>
+        <v>-0.3892</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.506</v>
+        <v>1.6092</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4582</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.506</v>
+        <v>0.1511</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0684</v>
+        <v>-0.9133</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1661</v>
+        <v>-0.7658</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0977</v>
+        <v>-0.1476</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1457</v>
@@ -1078,13 +1078,13 @@
         <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2858</v>
+        <v>-0.1307</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.424</v>
+        <v>-0.0236</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1382</v>
+        <v>-0.1071</v>
       </c>
       <c r="V8" t="n">
         <v>-1.025</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>A. JIMÉNEZ BARRETO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6148</v>
+        <v>-1.3292</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1204</v>
+        <v>-0.2067</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5057</v>
+        <v>-1.1226</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9508</v>
+        <v>0.8194</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0395</v>
+        <v>0.2043</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9903</v>
+        <v>0.6151</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6692</v>
+        <v>1.3815</v>
       </c>
       <c r="K9" t="n">
-        <v>1.31</v>
+        <v>0.0824</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9792</v>
+        <v>1.2991</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2816</v>
+        <v>-0.5621</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2704</v>
+        <v>0.1219</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0111</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.7761</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.9403</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.1642</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.2187</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.506</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-2.1344</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.1344</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-1.2732</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.775</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.4982</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.6092</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.4582</v>
-      </c>
       <c r="X9" t="n">
-        <v>0.1511</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.636</v>
+        <v>-3.627</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4181</v>
+        <v>-2.5182</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2179</v>
+        <v>-1.1089</v>
       </c>
       <c r="G10" t="n">
         <v>0.9368</v>
@@ -1234,13 +1234,13 @@
         <v>2.5224</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4847</v>
+        <v>-0.4758</v>
       </c>
       <c r="T10" t="n">
-        <v>0.074</v>
+        <v>-0.0261</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5588</v>
+        <v>-0.4497</v>
       </c>
       <c r="V10" t="n">
         <v>-2.7298</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8981</v>
+        <v>-6.6286</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3382</v>
+        <v>-5.096</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5599</v>
+        <v>-1.5326</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2889</v>
@@ -1312,13 +1312,13 @@
         <v>1.9403</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1516</v>
+        <v>0.4212</v>
       </c>
       <c r="T11" t="n">
-        <v>0.268</v>
+        <v>0.5103</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1164</v>
+        <v>-0.0891</v>
       </c>
       <c r="V11" t="n">
         <v>-2.6265</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.3444</v>
+        <v>-7.3962</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2367</v>
+        <v>-4.3158</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1077</v>
+        <v>-3.0805</v>
       </c>
       <c r="G12" t="n">
         <v>1.8494</v>
@@ -1390,13 +1390,13 @@
         <v>2.7164</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.952</v>
+        <v>-1.0038</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2412</v>
+        <v>-0.3202</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7108</v>
+        <v>-0.6836</v>
       </c>
       <c r="V12" t="n">
         <v>-4.9433</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.7912</v>
+        <v>-14.5797</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.753</v>
+        <v>-11.542</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0381</v>
+        <v>-3.038099999999999</v>
       </c>
       <c r="G13" t="n">
         <v>4.7846</v>
@@ -1456,7 +1456,7 @@
         <v>-5.1906</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5559999999999998</v>
+        <v>0.5559999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-4.8507</v>
@@ -1468,13 +1468,13 @@
         <v>22.3138</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2731</v>
+        <v>-0.06170000000000053</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0427</v>
+        <v>2.2542</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.3158</v>
+        <v>-2.3157</v>
       </c>
       <c r="V13" t="n">
         <v>-14.4521</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.645</v>
+        <v>7.1088</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0303</v>
+        <v>4.9302</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6147</v>
+        <v>2.1786</v>
       </c>
       <c r="G14" t="n">
         <v>1.7648</v>
@@ -1546,13 +1546,13 @@
         <v>4.2687</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1332</v>
+        <v>0.3306</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2445</v>
+        <v>0.1444</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3777</v>
+        <v>0.1862</v>
       </c>
       <c r="V14" t="n">
         <v>5.7895</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0366</v>
+        <v>4.0276</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0735</v>
+        <v>1.7732</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9631</v>
+        <v>2.2545</v>
       </c>
       <c r="G15" t="n">
         <v>-1.7758</v>
@@ -1624,13 +1624,13 @@
         <v>2.7164</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3154</v>
+        <v>0.3065</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4262</v>
+        <v>0.1259</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1108</v>
+        <v>0.1806</v>
       </c>
       <c r="V15" t="n">
         <v>5.8851</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6491</v>
+        <v>3.4387</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4875</v>
+        <v>2.1911</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1616</v>
+        <v>1.2476</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7566</v>
+        <v>1.3637</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.388</v>
+        <v>0.1219</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3686</v>
+        <v>1.2418</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1428</v>
+        <v>2.2389</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7374000000000001</v>
+        <v>1.6477</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.8802</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6138</v>
+        <v>-0.8752</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1254</v>
+        <v>-1.5258</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.6506</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0.3881</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.8806</v>
+        <v>-1.1642</v>
       </c>
       <c r="R16" t="n">
-        <v>3.8806</v>
+        <v>1.5523</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1222</v>
+        <v>0.4153</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2752</v>
+        <v>0.2223</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.153</v>
+        <v>0.1929</v>
       </c>
       <c r="V16" t="n">
-        <v>4.2836</v>
+        <v>1.2716</v>
       </c>
       <c r="W16" t="n">
-        <v>4.2358</v>
+        <v>0.894</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0478</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0717</v>
+        <v>3.1637</v>
       </c>
       <c r="E17" t="n">
-        <v>2.091</v>
+        <v>-0.2132</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9807</v>
+        <v>3.3768</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3637</v>
+        <v>-1.7566</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1219</v>
+        <v>-0.388</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2418</v>
+        <v>-1.3686</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2389</v>
+        <v>-1.1428</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6477</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5911999999999999</v>
+        <v>-1.8802</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8752</v>
+        <v>-0.6138</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5258</v>
+        <v>-1.1254</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6506</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3881</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1642</v>
+        <v>-3.8806</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5523</v>
+        <v>3.8806</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0482</v>
+        <v>0.6368</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1222</v>
+        <v>0.5745</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.074</v>
+        <v>0.0623</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2716</v>
+        <v>4.2836</v>
       </c>
       <c r="W17" t="n">
-        <v>0.894</v>
+        <v>4.2358</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3776</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0213</v>
+        <v>2.6943</v>
       </c>
       <c r="E18" t="n">
         <v>-1.1996</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2209</v>
+        <v>3.8938</v>
       </c>
       <c r="G18" t="n">
         <v>1.5329</v>
@@ -1858,13 +1858,13 @@
         <v>3.2985</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1519</v>
+        <v>-0.4789</v>
       </c>
       <c r="T18" t="n">
         <v>0.0011</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.153</v>
+        <v>-0.48</v>
       </c>
       <c r="V18" t="n">
         <v>0.2821</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7305</v>
+        <v>2.2165</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0954</v>
+        <v>0.5052</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8259</v>
+        <v>1.7113</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7309</v>
@@ -1936,13 +1936,13 @@
         <v>3.2985</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7629</v>
+        <v>1.2489</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2412</v>
+        <v>0.3594</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0041</v>
+        <v>0.8894</v>
       </c>
       <c r="V19" t="n">
         <v>0.5642</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1233</v>
+        <v>1.4781</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2367</v>
+        <v>0.537</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8867</v>
+        <v>0.9412</v>
       </c>
       <c r="G20" t="n">
         <v>0.0439</v>
@@ -2014,13 +2014,13 @@
         <v>1.7463</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4729</v>
+        <v>-0.118</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2423</v>
+        <v>0.058</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2306</v>
+        <v>-0.1761</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0477</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.8222</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9691</v>
+        <v>0.9146</v>
       </c>
       <c r="G21" t="n">
         <v>0.0921</v>
@@ -2092,13 +2092,13 @@
         <v>2.5224</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6258</v>
+        <v>0.6704</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6386</v>
+        <v>0.7377</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0128</v>
+        <v>-0.0673</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2821</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2025</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8779</v>
+        <v>-1.3774</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6754</v>
+        <v>0.5664</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1061</v>
@@ -2170,13 +2170,13 @@
         <v>1.9403</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2308</v>
+        <v>0.1607</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3634</v>
+        <v>0.1371</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1326</v>
+        <v>0.0236</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8358</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3314</v>
+        <v>-5.6157</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7867</v>
+        <v>-3.2862</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5448</v>
+        <v>-2.3295</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2127</v>
@@ -2248,13 +2248,13 @@
         <v>1.9403</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6128</v>
+        <v>0.1029</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5451</v>
+        <v>-0.0446</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0677</v>
+        <v>0.1475</v>
       </c>
       <c r="V23" t="n">
         <v>-1.506</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>15.7913</v>
+        <v>17.7933</v>
       </c>
       <c r="E24" t="n">
         <v>3.038100000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>12.7533</v>
+        <v>14.7553</v>
       </c>
       <c r="G24" t="n">
         <v>-4.7847</v>
@@ -2326,13 +2326,13 @@
         <v>27.1643</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2729</v>
+        <v>3.2752</v>
       </c>
       <c r="T24" t="n">
         <v>2.3158</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0429</v>
+        <v>0.9591</v>
       </c>
       <c r="V24" t="n">
         <v>14.4522</v>
